--- a/data/trans_dic/P1435_2011_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1435_2011_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,18</t>
+          <t>0,21; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,06</t>
+          <t>1,39; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,91</t>
+          <t>2,8; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,77</t>
+          <t>9,03; 12,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,2</t>
+          <t>1,85; 3,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,39</t>
+          <t>6,11; 8,48</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,04</t>
+          <t>0,95; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,37</t>
+          <t>2,54; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 39,72</t>
+          <t>7,44; 9,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,24</t>
+          <t>1,32; 2,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 24,42</t>
+          <t>4,3; 5,5</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,12</t>
+          <t>1,17; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,1</t>
+          <t>2,21; 5,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,7</t>
+          <t>6,64; 10,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,11</t>
+          <t>1,17; 3,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,52</t>
+          <t>4,29; 6,36</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -872,22 +872,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,55</t>
+          <t>0,17; 0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,21</t>
+          <t>1,3; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,31</t>
+          <t>2,96; 4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 30,29</t>
+          <t>8,17; 9,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 18,3</t>
+          <t>4,92; 5,87</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>101086</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2080; 11534</t>
+          <t>2010; 11356</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7651; 20875</t>
+          <t>8042; 22142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37874; 65747</t>
+          <t>37473; 66761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70029; 103587</t>
+          <t>74119; 103086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42977; 73986</t>
+          <t>42669; 70602</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82661; 118950</t>
+          <t>85395; 118540</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364704</t>
+          <t>183176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>396173</t>
+          <t>214934</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1886; 10576</t>
+          <t>1900; 10610</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20716; 46738</t>
+          <t>21078; 48013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44984; 76754</t>
+          <t>44570; 75673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168264; 887926</t>
+          <t>161339; 207562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49746; 83401</t>
+          <t>49271; 80581</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192521; 1104903</t>
+          <t>188931; 241967</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>61315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>75235</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5823</t>
+          <t>0; 5763</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6740; 20169</t>
+          <t>8317; 24497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10524; 27967</t>
+          <t>10150; 27221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45507; 70560</t>
+          <t>48627; 75773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10651; 29217</t>
+          <t>10982; 29249</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57331; 85205</t>
+          <t>61891; 91850</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>505758</t>
+          <t>331681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>562335</t>
+          <t>391255</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5864; 18653</t>
+          <t>5935; 18982</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40171; 76093</t>
+          <t>45846; 77982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105663; 153095</t>
+          <t>105267; 152314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>309761; 1104685</t>
+          <t>304098; 362906</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>115227; 163331</t>
+          <t>114841; 163302</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>356175; 1299004</t>
+          <t>356128; 425285</t>
         </is>
       </c>
     </row>
